--- a/Projects/CmF_SHG_Women_Entrepreneurs/reports/excel_exports/4_Demographics_and_Survey_Indicators.xlsx
+++ b/Projects/CmF_SHG_Women_Entrepreneurs/reports/excel_exports/4_Demographics_and_Survey_Indicators.xlsx
@@ -532,7 +532,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>General &amp; Demographic Indicators of Women Entrepreneurs (All Rajasthan District)</t>
+          <t>General &amp; Demographic Indicators of Women Entrepreneurs (Dausa District)</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3"/>
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="6">
@@ -592,7 +592,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="7">
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
@@ -653,10 +653,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="12">
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.3035714285714285</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="16">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="17">
@@ -733,7 +733,7 @@
         <v>14</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="18">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="22">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.9821428571428571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="24">
@@ -823,7 +823,7 @@
         <v>2</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="25">
@@ -836,7 +836,7 @@
         <v>3</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0.05357142857142857</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="26">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="28">
@@ -913,7 +913,7 @@
         <v>2</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="32">
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="33">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>0.375</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="34">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="35">
@@ -965,7 +965,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="36">
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>0.9107142857142857</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -1042,7 +1042,7 @@
         <v>3</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0.05357142857142857</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="42">
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.3214285714285715</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="48">
@@ -1132,7 +1132,7 @@
         <v>3</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>0.05357142857142857</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="49">
@@ -1145,7 +1145,7 @@
         <v>22</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0.3928571428571428</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="50">
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.1964285714285714</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="51">
@@ -1209,7 +1209,7 @@
         <v>6</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="55">
@@ -1222,7 +1222,7 @@
         <v>1</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="56">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="57">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="C57" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="58">
@@ -1261,7 +1261,7 @@
         <v>12</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="59">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="C59" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>0.1607142857142857</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="60">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="C61" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="62">
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>0.3928571428571428</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="67">
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="C67" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="68">
@@ -1390,7 +1390,7 @@
         <v>4</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="69">
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="70">
@@ -1416,7 +1416,7 @@
         <v>1</v>
       </c>
       <c r="D70" s="7" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="71">
@@ -1467,7 +1467,7 @@
         <v>2</v>
       </c>
       <c r="D74" s="7" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="75">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="C75" s="6" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>0.5892857142857143</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="76">
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="77">
@@ -1506,7 +1506,7 @@
         <v>4</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="78">
@@ -1519,7 +1519,7 @@
         <v>1</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="79">
@@ -1596,7 +1596,7 @@
         <v>4</v>
       </c>
       <c r="D84" s="7" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="85">
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="C85" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>0.1607142857142857</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="86">
@@ -1622,7 +1622,7 @@
         <v>3</v>
       </c>
       <c r="D86" s="7" t="n">
-        <v>0.05357142857142857</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="87">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="C87" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="88">
@@ -1648,7 +1648,7 @@
         <v>1</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="89">
@@ -1661,7 +1661,7 @@
         <v>2</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="90">
@@ -1674,7 +1674,7 @@
         <v>1</v>
       </c>
       <c r="D90" s="7" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="91">
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="C91" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="92">
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D92" s="7" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="93">
@@ -1713,7 +1713,7 @@
         <v>15</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>0.2678571428571428</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="94">
@@ -1761,10 +1761,10 @@
         </is>
       </c>
       <c r="C97" s="6" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="98">
@@ -1774,10 +1774,10 @@
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D98" s="7" t="n">
-        <v>0.4464285714285715</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="99">
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="C99" s="6" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="100">
@@ -1829,7 +1829,7 @@
         <v>24</v>
       </c>
       <c r="D102" s="7" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="103">
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D104" s="7" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="105">
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="C105" s="6" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="106">
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D106" s="7" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="107">
@@ -1894,7 +1894,7 @@
         <v>5</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>0.08928571428571429</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="108">
@@ -1916,11 +1916,11 @@
           <t>Mudra loan</t>
         </is>
       </c>
-      <c r="C109" s="6" t="n">
-        <v>1</v>
+      <c r="C109" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D109" s="7" t="n">
-        <v>0.01785714285714286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -1933,7 +1933,7 @@
         <v>1</v>
       </c>
       <c r="D110" s="7" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="111">
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D114" s="7" t="n">
-        <v>0.6964285714285714</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="115">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="C115" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>0.2321428571428572</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="116">
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="C116" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D116" s="7" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="117">
@@ -2023,7 +2023,7 @@
         <v>6</v>
       </c>
       <c r="D117" s="7" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="118">
@@ -2036,7 +2036,7 @@
         <v>7</v>
       </c>
       <c r="D118" s="7" t="n">
-        <v>0.125</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="119">
@@ -2049,7 +2049,7 @@
         <v>21</v>
       </c>
       <c r="D119" s="7" t="n">
-        <v>0.375</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="120">
@@ -2062,7 +2062,7 @@
         <v>5</v>
       </c>
       <c r="D120" s="7" t="n">
-        <v>0.08928571428571429</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="121">
@@ -2075,7 +2075,7 @@
         <v>2</v>
       </c>
       <c r="D121" s="7" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="122">
@@ -2088,7 +2088,7 @@
         <v>2</v>
       </c>
       <c r="D122" s="7" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="123">
@@ -2101,7 +2101,7 @@
         <v>6</v>
       </c>
       <c r="D123" s="7" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="124">
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D124" s="7" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="125">
@@ -2165,7 +2165,7 @@
         <v>20</v>
       </c>
       <c r="D128" s="7" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="129">
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="C129" s="6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="130">
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D130" s="7" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="131">
@@ -2217,7 +2217,7 @@
         <v>10</v>
       </c>
       <c r="D132" s="7" t="n">
-        <v>0.1785714285714286</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="133">
@@ -2230,7 +2230,7 @@
         <v>1</v>
       </c>
       <c r="D133" s="7" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="134">
@@ -2243,7 +2243,7 @@
         <v>2</v>
       </c>
       <c r="D134" s="7" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="135">
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D138" s="7" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="139">
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="C139" s="6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D139" s="7" t="n">
-        <v>0.3928571428571428</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="140">
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D140" s="7" t="n">
-        <v>0.4821428571428572</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="141">
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="C141" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D141" s="7" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="142">
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D142" s="7" t="n">
-        <v>0.1964285714285714</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="143">
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="C143" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D143" s="7" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="144">
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="C144" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D144" s="7" t="n">
-        <v>0.3035714285714285</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="145">
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="C148" s="6" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D148" s="7" t="n">
-        <v>0.625</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="149">
@@ -2436,7 +2436,7 @@
         <v>15</v>
       </c>
       <c r="D149" s="7" t="n">
-        <v>0.2678571428571428</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="150">
@@ -2449,7 +2449,7 @@
         <v>2</v>
       </c>
       <c r="D150" s="7" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="151">
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="C157" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D157" s="7" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="158">
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D158" s="7" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="159">
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D162" s="7" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="163">
@@ -2616,7 +2616,7 @@
         <v>1</v>
       </c>
       <c r="D163" s="7" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="164">
@@ -2667,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="D167" s="7" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="168">
@@ -2680,7 +2680,7 @@
         <v>5</v>
       </c>
       <c r="D168" s="7" t="n">
-        <v>0.08928571428571429</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="169">
@@ -2706,7 +2706,7 @@
         <v>2</v>
       </c>
       <c r="D170" s="7" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="171">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="C172" s="6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D172" s="7" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="173">
@@ -2745,7 +2745,7 @@
         <v>2</v>
       </c>
       <c r="D173" s="7" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="174">
@@ -2796,7 +2796,7 @@
         <v>1</v>
       </c>
       <c r="D177" s="7" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="178">
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="C178" s="6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D178" s="7" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="179">
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="C179" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D179" s="7" t="n">
-        <v>0.4464285714285715</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="180">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="C180" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D180" s="7" t="n">
-        <v>0.5178571428571429</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="181">
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="C181" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D181" s="7" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="182">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="C182" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D182" s="7" t="n">
-        <v>0.1964285714285714</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="183">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="C183" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D183" s="7" t="n">
-        <v>0.4464285714285715</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="184">
@@ -2887,7 +2887,7 @@
         <v>7</v>
       </c>
       <c r="D184" s="7" t="n">
-        <v>0.125</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="185">
@@ -2900,7 +2900,7 @@
         <v>4</v>
       </c>
       <c r="D185" s="7" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="186">
@@ -2913,7 +2913,7 @@
         <v>4</v>
       </c>
       <c r="D186" s="7" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="187">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="C190" s="6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D190" s="7" t="n">
-        <v>0.6607142857142857</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="191">
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="C191" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D191" s="7" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="192">
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="C192" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D192" s="7" t="n">
-        <v>0.2678571428571428</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="193">
@@ -3003,7 +3003,7 @@
         <v>15</v>
       </c>
       <c r="D193" s="7" t="n">
-        <v>0.2678571428571428</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="194">
@@ -3016,7 +3016,7 @@
         <v>3</v>
       </c>
       <c r="D194" s="7" t="n">
-        <v>0.05357142857142857</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="195">
@@ -3029,7 +3029,7 @@
         <v>5</v>
       </c>
       <c r="D195" s="7" t="n">
-        <v>0.08928571428571429</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="196">
@@ -3042,7 +3042,7 @@
         <v>8</v>
       </c>
       <c r="D196" s="7" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="197">
@@ -3055,7 +3055,7 @@
         <v>7</v>
       </c>
       <c r="D197" s="7" t="n">
-        <v>0.125</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="198">
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="C201" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D201" s="7" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="202">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="C202" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D202" s="7" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="203">
@@ -3132,7 +3132,7 @@
         <v>10</v>
       </c>
       <c r="D203" s="7" t="n">
-        <v>0.1785714285714286</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="204">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="C207" s="6" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D207" s="7" t="n">
-        <v>0.5535714285714286</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="208">
@@ -3196,7 +3196,7 @@
         <v>21</v>
       </c>
       <c r="D208" s="7" t="n">
-        <v>0.375</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="209">
@@ -3247,7 +3247,7 @@
         <v>6</v>
       </c>
       <c r="D212" s="7" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="213">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="C213" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D213" s="7" t="n">
-        <v>0.2321428571428572</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="214">
@@ -3273,7 +3273,7 @@
         <v>9</v>
       </c>
       <c r="D214" s="7" t="n">
-        <v>0.1607142857142857</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="215">
@@ -3286,7 +3286,7 @@
         <v>3</v>
       </c>
       <c r="D215" s="7" t="n">
-        <v>0.05357142857142857</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="216">
@@ -3350,7 +3350,7 @@
         <v>12</v>
       </c>
       <c r="D220" s="7" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="221">
@@ -3359,11 +3359,11 @@
           <t>I regularly share images/reels on instagram to get orders</t>
         </is>
       </c>
-      <c r="C221" s="6" t="n">
-        <v>1</v>
+      <c r="C221" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D221" s="7" t="n">
-        <v>0.01785714285714286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -3376,7 +3376,7 @@
         <v>2</v>
       </c>
       <c r="D222" s="7" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="223">
@@ -3389,7 +3389,7 @@
         <v>4</v>
       </c>
       <c r="D223" s="7" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="224">
@@ -3402,7 +3402,7 @@
         <v>3</v>
       </c>
       <c r="D224" s="7" t="n">
-        <v>0.05357142857142857</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="225">
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="C225" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D225" s="7" t="n">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="226">
@@ -3428,7 +3428,7 @@
         <v>9</v>
       </c>
       <c r="D226" s="7" t="n">
-        <v>0.1607142857142857</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="227">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="C230" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D230" s="7" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="231">
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="C231" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D231" s="7" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="232">
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="C235" s="6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D235" s="7" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="236">
@@ -3595,7 +3595,7 @@
         <v>7</v>
       </c>
       <c r="D239" s="7" t="n">
-        <v>0.125</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="240">
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="C240" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D240" s="7" t="n">
-        <v>0.1607142857142857</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="241">
@@ -3621,7 +3621,7 @@
         <v>4</v>
       </c>
       <c r="D241" s="7" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="242">
@@ -3634,7 +3634,7 @@
         <v>5</v>
       </c>
       <c r="D242" s="7" t="n">
-        <v>0.08928571428571429</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="243">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="C247" s="14" t="inlineStr">
         <is>
-          <t>3.8 Years</t>
+          <t>3.7 Years</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="C248" s="14" t="inlineStr">
         <is>
-          <t>3.0 Years</t>
+          <t>2.9 Years</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="C249" s="14" t="inlineStr">
         <is>
-          <t>4.6 Years</t>
+          <t>4.5 Years</t>
         </is>
       </c>
     </row>
